--- a/Projects/Player-Template.xlsx
+++ b/Projects/Player-Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049AF519-819D-4A4C-870B-5E6285808908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87166C91-8276-ED43-906A-21AE73BB4F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="7" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="8" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Advanced Shooting" sheetId="6" r:id="rId6"/>
     <sheet name="Play-by-Play" sheetId="7" r:id="rId7"/>
     <sheet name="Shooting" sheetId="8" r:id="rId8"/>
+    <sheet name="Resources" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Season</t>
   </si>
@@ -370,6 +371,9 @@
   </si>
   <si>
     <t>Md._1/2-Court</t>
+  </si>
+  <si>
+    <t>URL</t>
   </si>
 </sst>
 </file>
@@ -4668,4 +4672,19 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14762BC1-65B5-C644-A935-CED54EC76738}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Projects/Player-Template.xlsx
+++ b/Projects/Player-Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87166C91-8276-ED43-906A-21AE73BB4F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2E56A7-FE87-144B-8256-F350104F8E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="8" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="39420" yWindow="1400" windowWidth="30240" windowHeight="17680" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,13 @@
     <sheet name="Per 36" sheetId="3" r:id="rId3"/>
     <sheet name="Per 100 Poss" sheetId="4" r:id="rId4"/>
     <sheet name="Advanced" sheetId="5" r:id="rId5"/>
-    <sheet name="Advanced Shooting" sheetId="6" r:id="rId6"/>
+    <sheet name="Adjusted Shooting" sheetId="6" r:id="rId6"/>
     <sheet name="Play-by-Play" sheetId="7" r:id="rId7"/>
     <sheet name="Shooting" sheetId="8" r:id="rId8"/>
-    <sheet name="Resources" sheetId="9" r:id="rId9"/>
+    <sheet name="Game Highs" sheetId="11" r:id="rId9"/>
+    <sheet name="Playoff Series" sheetId="10" r:id="rId10"/>
+    <sheet name="College Stats" sheetId="12" r:id="rId11"/>
+    <sheet name="Resources" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="146">
   <si>
     <t>Season</t>
   </si>
@@ -374,6 +377,114 @@
   </si>
   <si>
     <t>URL</t>
+  </si>
+  <si>
+    <t>Tm</t>
+  </si>
+  <si>
+    <t>GmSc</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Opp</t>
+  </si>
+  <si>
+    <t>W/L</t>
+  </si>
+  <si>
+    <t>MP_Per Game</t>
+  </si>
+  <si>
+    <t>PTS_Per Game</t>
+  </si>
+  <si>
+    <t>TRB_Per Game</t>
+  </si>
+  <si>
+    <t>AST_Per Game</t>
+  </si>
+  <si>
+    <t>STL_Per Game</t>
+  </si>
+  <si>
+    <t>BLK_Per Game</t>
+  </si>
+  <si>
+    <t>FG_Totals</t>
+  </si>
+  <si>
+    <t>FGA_Totals</t>
+  </si>
+  <si>
+    <t>FG%_Totals</t>
+  </si>
+  <si>
+    <t>3P_Totals</t>
+  </si>
+  <si>
+    <t>3PA_Totals</t>
+  </si>
+  <si>
+    <t>3P%_Totals</t>
+  </si>
+  <si>
+    <t>2P_Totals</t>
+  </si>
+  <si>
+    <t>2PA_Totals</t>
+  </si>
+  <si>
+    <t>2P%_Totals</t>
+  </si>
+  <si>
+    <t>eFG%_Totals</t>
+  </si>
+  <si>
+    <t>FT_Totals</t>
+  </si>
+  <si>
+    <t>FTA_Totals</t>
+  </si>
+  <si>
+    <t>FT%_Totals</t>
+  </si>
+  <si>
+    <t>ORB_Totals</t>
+  </si>
+  <si>
+    <t>DRB_Totals</t>
+  </si>
+  <si>
+    <t>TRB_Totals</t>
+  </si>
+  <si>
+    <t>AST_Totals</t>
+  </si>
+  <si>
+    <t>STL_Totals</t>
+  </si>
+  <si>
+    <t>BLK_Totals</t>
+  </si>
+  <si>
+    <t>TOV_Totals</t>
+  </si>
+  <si>
+    <t>PF_Totals</t>
+  </si>
+  <si>
+    <t>PTS_Totals</t>
+  </si>
+  <si>
+    <t>College</t>
+  </si>
+  <si>
+    <t>G_Totals</t>
+  </si>
+  <si>
+    <t>MP_Totals</t>
   </si>
 </sst>
 </file>
@@ -1292,6 +1403,298 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADB7185-16E3-8549-80FC-14BF9683AAD0}">
+  <dimension ref="A1:AK1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A28CC5-B1D2-3340-AB41-89879FBDB32E}">
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14762BC1-65B5-C644-A935-CED54EC76738}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7B71AE-6323-D144-8F47-24F113ED928D}">
   <dimension ref="A1:AF12"/>
@@ -4675,13 +5078,104 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14762BC1-65B5-C644-A935-CED54EC76738}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57849F4F-AFA6-5543-9E4D-A8AEBB9E5B7A}">
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>109</v>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Projects/Player-Template.xlsx
+++ b/Projects/Player-Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2E56A7-FE87-144B-8256-F350104F8E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65683F22-BB51-784D-AD89-2B200D43C572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39420" yWindow="1400" windowWidth="30240" windowHeight="17680" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>

--- a/Projects/Player-Template.xlsx
+++ b/Projects/Player-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65683F22-BB51-784D-AD89-2B200D43C572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F01BE1E-F775-5147-919B-492FA9061F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
@@ -907,35 +907,34 @@
   <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1071,7 +1070,7 @@
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1103,69 +1102,69 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="4"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -1713,11 +1712,11 @@
     <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -1868,7 +1867,7 @@
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1901,71 +1900,71 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="4"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -2226,18 +2225,17 @@
     <col min="9" max="9" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4.5" bestFit="1" customWidth="1"/>
@@ -2378,7 +2376,7 @@
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -2410,69 +2408,69 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="4"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
